--- a/Section 4.3/Data_section4.3.xlsx
+++ b/Section 4.3/Data_section4.3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Comsol_Tut\EquationBasedModelling\HTO_paper_models\latest_model_tcd\Neom_report_models\Publication Models\modified_model\Optimization_study\saved data\Joule_submission_docs\Data for section 3.3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KUNTEAM\Documents\GitHub\Physics-informed-multiscale-optimization-of-renewable-powered-alkaline-water-electrolysis\Section 4.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A3D903-ABC0-4500-BE7E-D37693428E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F03538-B237-4FD4-A85A-E1905783FC9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{7C88D86B-F107-4116-B17D-B8DFC6C89132}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="45">
   <si>
     <t>Fig. 6a</t>
   </si>
@@ -131,21 +131,9 @@
     <t>gr1.5</t>
   </si>
   <si>
-    <t>gr2.0</t>
-  </si>
-  <si>
-    <t>gr3.5</t>
-  </si>
-  <si>
     <t>gr3.0</t>
   </si>
   <si>
-    <t>gr2</t>
-  </si>
-  <si>
-    <t>gr3</t>
-  </si>
-  <si>
     <t>Effect of stack rated efficiency</t>
   </si>
   <si>
@@ -177,6 +165,12 @@
   </si>
   <si>
     <t>Note: Data for case medium degradation (m=0.001), 75% stack eff. and gr2 is the averaged data across 5 runs as calculated in section 4.2</t>
+  </si>
+  <si>
+    <t>gr2.5</t>
+  </si>
+  <si>
+    <t>gr4.0</t>
   </si>
 </sst>
 </file>
@@ -238,10 +232,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -576,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46B22FAD-FAB5-4B0C-86EB-973ECA5282AF}">
-  <dimension ref="J5:AN62"/>
+  <dimension ref="J5:AN59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="8" max="8" width="13.28515625" customWidth="1"/>
@@ -594,51 +588,51 @@
   </cols>
   <sheetData>
     <row r="5" spans="10:40" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3"/>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="3"/>
-      <c r="AE5" s="3"/>
-      <c r="AF5" s="3"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="4"/>
+      <c r="AA5" s="4"/>
+      <c r="AB5" s="4"/>
+      <c r="AC5" s="4"/>
+      <c r="AD5" s="4"/>
+      <c r="AE5" s="4"/>
+      <c r="AF5" s="4"/>
     </row>
     <row r="7" spans="10:40" x14ac:dyDescent="0.25">
       <c r="W7" t="s">
         <v>18</v>
       </c>
-      <c r="AB7" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC7" s="4"/>
-      <c r="AD7" s="4"/>
-      <c r="AE7" s="4"/>
-      <c r="AF7" s="4"/>
-      <c r="AG7" s="4"/>
-      <c r="AH7" s="4"/>
-      <c r="AI7" s="4"/>
-      <c r="AJ7" s="4"/>
-      <c r="AK7" s="4"/>
-      <c r="AL7" s="4"/>
-      <c r="AM7" s="4"/>
-      <c r="AN7" s="4"/>
+      <c r="AB7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="3"/>
+      <c r="AE7" s="3"/>
+      <c r="AF7" s="3"/>
+      <c r="AG7" s="3"/>
+      <c r="AH7" s="3"/>
+      <c r="AI7" s="3"/>
+      <c r="AJ7" s="3"/>
+      <c r="AK7" s="3"/>
+      <c r="AL7" s="3"/>
+      <c r="AM7" s="3"/>
+      <c r="AN7" s="3"/>
     </row>
     <row r="8" spans="10:40" x14ac:dyDescent="0.25">
       <c r="M8" s="1" t="s">
@@ -653,7 +647,7 @@
     </row>
     <row r="9" spans="10:40" x14ac:dyDescent="0.25">
       <c r="K9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="L9" t="s">
         <v>1</v>
@@ -676,16 +670,16 @@
     </row>
     <row r="10" spans="10:40" x14ac:dyDescent="0.25">
       <c r="K10">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="L10">
-        <v>7.8218100000000002</v>
+        <v>7.4375600000000004</v>
       </c>
       <c r="M10">
-        <v>7.7447055701440242</v>
+        <v>7.37</v>
       </c>
       <c r="N10">
-        <v>7.4387800000000004</v>
+        <v>7.3490700000000002</v>
       </c>
       <c r="R10" t="s">
         <v>6</v>
@@ -703,13 +697,13 @@
         <v>19</v>
       </c>
       <c r="Y10">
-        <v>7.7727000000000004</v>
+        <v>6.0723900000000004</v>
       </c>
       <c r="Z10">
-        <v>7.3896322613393437</v>
+        <v>6.6853800000000003</v>
       </c>
       <c r="AA10">
-        <v>7.0929500000000001</v>
+        <v>11.101229999999999</v>
       </c>
     </row>
     <row r="11" spans="10:40" x14ac:dyDescent="0.25">
@@ -717,37 +711,37 @@
         <v>8</v>
       </c>
       <c r="L11">
-        <v>7.72227</v>
+        <v>6.9819000000000004</v>
       </c>
       <c r="M11">
-        <v>7.5775588512345324</v>
+        <v>6.92096</v>
       </c>
       <c r="N11">
-        <v>7.3609799999999996</v>
+        <v>6.6698599999999999</v>
       </c>
       <c r="R11" t="s">
         <v>7</v>
       </c>
       <c r="S11">
-        <v>28.09243</v>
+        <v>38.253450000000001</v>
       </c>
       <c r="T11">
-        <v>29.821680000000001</v>
+        <v>41.122970000000002</v>
       </c>
       <c r="U11">
-        <v>30.706399999999999</v>
+        <v>46.533920000000002</v>
       </c>
       <c r="X11" t="s">
         <v>20</v>
       </c>
       <c r="Y11">
-        <v>5.0199999999999996</v>
+        <v>4.83</v>
       </c>
       <c r="Z11">
-        <v>5.0379999999999994</v>
+        <v>4.84</v>
       </c>
       <c r="AA11">
-        <v>5.0199999999999996</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="12" spans="10:40" x14ac:dyDescent="0.25">
@@ -755,317 +749,275 @@
         <v>10</v>
       </c>
       <c r="L12">
-        <v>7.6676900000000003</v>
+        <v>6.9270399999999999</v>
       </c>
       <c r="M12">
-        <v>7.5073438785757585</v>
+        <v>6.8425500000000001</v>
       </c>
       <c r="N12">
-        <v>7.2600800000000003</v>
+        <v>6.5680800000000001</v>
       </c>
       <c r="R12" t="s">
         <v>8</v>
       </c>
       <c r="S12">
-        <v>78.397300000000001</v>
+        <v>70.729460000000003</v>
       </c>
       <c r="T12">
-        <v>78.329400000000007</v>
+        <v>69.133430000000004</v>
       </c>
       <c r="U12">
-        <v>71.170259999999999</v>
+        <v>68.877170000000007</v>
       </c>
       <c r="X12" t="s">
         <v>21</v>
       </c>
       <c r="Y12">
-        <v>0.7</v>
+        <v>0.4002</v>
       </c>
       <c r="Z12">
-        <v>0.70000252109706307</v>
+        <v>0.40848000000000001</v>
       </c>
       <c r="AA12">
-        <v>0.70001999999999998</v>
+        <v>0.58177000000000001</v>
       </c>
     </row>
     <row r="13" spans="10:40" x14ac:dyDescent="0.25">
       <c r="K13">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L13">
-        <v>7.6508599999999998</v>
+        <v>6.85745</v>
       </c>
       <c r="M13">
-        <v>7.4745317893238576</v>
+        <v>6.7597699999999996</v>
       </c>
       <c r="N13">
-        <v>7.2272699999999999</v>
+        <v>6.4794299999999998</v>
       </c>
       <c r="R13" t="s">
         <v>9</v>
       </c>
       <c r="S13">
-        <v>14.230040000000001</v>
+        <v>25.050889999999999</v>
       </c>
       <c r="T13">
-        <v>11.230370000000001</v>
+        <v>21.321850000000001</v>
       </c>
       <c r="U13">
-        <v>2.01363</v>
+        <v>6.5405499999999996</v>
       </c>
       <c r="X13" t="s">
         <v>22</v>
       </c>
       <c r="Y13">
-        <v>5.8188500000000003</v>
+        <v>5.3824500000000004</v>
       </c>
       <c r="Z13">
-        <v>5.3582015232979883</v>
+        <v>5.8800100000000004</v>
       </c>
       <c r="AA13">
-        <v>5.3649399999999998</v>
+        <v>10.45936</v>
       </c>
     </row>
     <row r="14" spans="10:40" x14ac:dyDescent="0.25">
       <c r="K14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L14">
-        <v>7.5990200000000003</v>
+        <v>6.8112000000000004</v>
       </c>
       <c r="M14">
-        <v>7.4252232347610185</v>
+        <v>6.69834</v>
       </c>
       <c r="N14">
-        <v>7.1649000000000003</v>
+        <v>6.4105299999999996</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
       </c>
       <c r="S14">
-        <v>39.268149999999999</v>
+        <v>55.055320000000002</v>
       </c>
       <c r="T14">
-        <v>39.344529999999999</v>
+        <v>55.101210000000002</v>
       </c>
       <c r="U14">
-        <v>39.357939999999999</v>
+        <v>55.195180000000001</v>
       </c>
       <c r="X14" t="s">
         <v>23</v>
       </c>
       <c r="Y14">
-        <v>0.75</v>
+        <v>1.3826700000000001</v>
       </c>
       <c r="Z14">
-        <v>0.75005655390372228</v>
+        <v>1.3183</v>
       </c>
       <c r="AA14">
-        <v>0.75016000000000005</v>
+        <v>0.75090000000000001</v>
       </c>
     </row>
     <row r="15" spans="10:40" x14ac:dyDescent="0.25">
       <c r="K15">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L15">
-        <v>7.5790199999999999</v>
+        <v>6.7887599999999999</v>
       </c>
       <c r="M15">
-        <v>7.4129670130295331</v>
+        <v>6.6696999999999997</v>
       </c>
       <c r="N15">
-        <v>7.12941</v>
+        <v>6.3943599999999998</v>
       </c>
       <c r="R15" t="s">
         <v>11</v>
       </c>
       <c r="S15">
-        <v>63.439169999999997</v>
+        <v>63.226979999999998</v>
       </c>
       <c r="T15">
-        <v>63.386830000000003</v>
+        <v>63.117829999999998</v>
       </c>
       <c r="U15">
-        <v>63.152149999999999</v>
+        <v>62.80397</v>
       </c>
       <c r="X15" t="s">
         <v>26</v>
       </c>
       <c r="Y15">
-        <v>2.0329899999999999</v>
+        <v>2.7279300000000002</v>
       </c>
       <c r="Z15">
-        <v>3.0017182478681526</v>
+        <v>2.3873000000000002</v>
       </c>
       <c r="AA15">
-        <v>2.7534200000000002</v>
+        <v>2.0087799999999998</v>
       </c>
     </row>
     <row r="16" spans="10:40" x14ac:dyDescent="0.25">
       <c r="K16">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="L16">
-        <v>7.56454</v>
+        <v>6.7667200000000003</v>
       </c>
       <c r="M16">
-        <v>7.4020784811407223</v>
+        <v>6.6479200000000001</v>
       </c>
       <c r="N16">
-        <v>7.10982</v>
+        <v>6.39358</v>
       </c>
       <c r="R16" t="s">
         <v>12</v>
       </c>
       <c r="S16">
-        <v>81.06</v>
+        <v>81.402069999999995</v>
       </c>
       <c r="T16">
-        <v>80.708179999999999</v>
+        <v>80.956599999999995</v>
       </c>
       <c r="U16">
-        <v>80.521039999999999</v>
+        <v>80.239549999999994</v>
       </c>
       <c r="X16" t="s">
         <v>24</v>
       </c>
       <c r="Y16">
-        <v>0.5</v>
+        <v>0.94</v>
       </c>
       <c r="Z16">
-        <v>0.52247943359597593</v>
+        <v>0.83</v>
       </c>
       <c r="AA16">
-        <v>0.60597000000000001</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="17" spans="10:32" x14ac:dyDescent="0.25">
       <c r="K17">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L17">
-        <v>7.5529500000000001</v>
+        <v>6.7649100000000004</v>
       </c>
       <c r="M17">
-        <v>7.3834216959521939</v>
+        <v>6.6489099999999999</v>
       </c>
       <c r="N17">
-        <v>7.0870699999999998</v>
+        <v>6.3994099999999996</v>
       </c>
       <c r="X17" t="s">
         <v>25</v>
       </c>
       <c r="Y17">
-        <v>12.10012</v>
+        <v>10.6511</v>
       </c>
       <c r="Z17">
-        <v>11.680091671013253</v>
+        <v>11.41943</v>
       </c>
       <c r="AA17">
-        <v>11.05461</v>
+        <v>12.95083</v>
       </c>
     </row>
     <row r="18" spans="10:32" x14ac:dyDescent="0.25">
       <c r="K18">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="L18">
-        <v>7.5607800000000003</v>
+        <v>6.7720599999999997</v>
       </c>
       <c r="M18">
-        <v>7.3871733367021379</v>
+        <v>6.6589299999999998</v>
       </c>
       <c r="N18">
-        <v>7.0959099999999999</v>
+        <v>6.4046000000000003</v>
       </c>
     </row>
     <row r="19" spans="10:32" x14ac:dyDescent="0.25">
       <c r="K19">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L19">
-        <v>7.5612899999999996</v>
+        <v>6.7800500000000001</v>
       </c>
       <c r="M19">
-        <v>7.4049464311515276</v>
+        <v>6.6846800000000002</v>
       </c>
       <c r="N19">
-        <v>7.1133800000000003</v>
-      </c>
-    </row>
-    <row r="20" spans="10:32" x14ac:dyDescent="0.25">
-      <c r="K20">
-        <v>28</v>
-      </c>
-      <c r="L20">
-        <v>7.5799899999999996</v>
-      </c>
-      <c r="M20">
-        <v>7.4351157426919654</v>
-      </c>
-      <c r="N20">
-        <v>7.1412800000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="10:32" x14ac:dyDescent="0.25">
-      <c r="K21">
-        <v>30</v>
-      </c>
-      <c r="L21">
-        <v>7.5941299999999998</v>
-      </c>
-      <c r="M21">
-        <v>7.4547209434987654</v>
-      </c>
-      <c r="N21">
-        <v>7.1610399999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="10:32" x14ac:dyDescent="0.25">
-      <c r="K22">
-        <v>35</v>
-      </c>
-      <c r="L22">
-        <v>7.6393199999999997</v>
-      </c>
-      <c r="M22">
-        <v>7.5061336356262522</v>
-      </c>
-      <c r="N22">
-        <v>7.2143300000000004</v>
+        <v>6.4372800000000003</v>
       </c>
     </row>
     <row r="26" spans="10:32" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="J26" s="3" t="s">
+      <c r="J26" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
-      <c r="Z26" s="3"/>
-      <c r="AA26" s="3"/>
-      <c r="AB26" s="3"/>
-      <c r="AC26" s="3"/>
-      <c r="AD26" s="3"/>
-      <c r="AE26" s="3"/>
-      <c r="AF26" s="3"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="4"/>
+      <c r="X26" s="4"/>
+      <c r="Y26" s="4"/>
+      <c r="Z26" s="4"/>
+      <c r="AA26" s="4"/>
+      <c r="AB26" s="4"/>
+      <c r="AC26" s="4"/>
+      <c r="AD26" s="4"/>
+      <c r="AE26" s="4"/>
+      <c r="AF26" s="4"/>
     </row>
     <row r="27" spans="10:32" x14ac:dyDescent="0.25">
       <c r="M27" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="S27" s="1" t="s">
         <v>29</v>
@@ -1076,43 +1028,43 @@
     </row>
     <row r="28" spans="10:32" x14ac:dyDescent="0.25">
       <c r="K28" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L28" t="s">
         <v>30</v>
       </c>
       <c r="M28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N28" t="s">
         <v>31</v>
       </c>
-      <c r="N28" t="s">
-        <v>32</v>
-      </c>
       <c r="O28" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="S28" t="s">
         <v>30</v>
       </c>
       <c r="T28" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="U28" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V28" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="Y28" t="s">
         <v>30</v>
       </c>
       <c r="Z28" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="AA28" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB28" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="10:32" x14ac:dyDescent="0.25">
@@ -1123,60 +1075,60 @@
         <v>19</v>
       </c>
       <c r="Y29">
-        <v>7.5964200000000002</v>
+        <v>6.8443399999999999</v>
       </c>
       <c r="Z29">
-        <v>7.3896322613393437</v>
+        <v>6.7962899999999999</v>
       </c>
       <c r="AA29">
-        <v>5.0232599999999996</v>
+        <v>6.6853800000000003</v>
       </c>
       <c r="AB29">
-        <v>5.41242</v>
+        <v>5.9179399999999998</v>
       </c>
     </row>
     <row r="30" spans="10:32" x14ac:dyDescent="0.25">
       <c r="K30">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="L30">
-        <v>8.47072</v>
+        <v>8.4897899999999993</v>
       </c>
       <c r="M30">
-        <v>7.7447055701440242</v>
+        <v>7.4814600000000002</v>
       </c>
       <c r="N30">
-        <v>7.55586</v>
+        <v>7.3700799999999997</v>
       </c>
       <c r="O30">
-        <v>7.4204100000000004</v>
+        <v>7.7894899999999998</v>
       </c>
       <c r="R30" t="s">
         <v>7</v>
       </c>
       <c r="S30">
-        <v>22.592130000000001</v>
+        <v>21.584810000000001</v>
       </c>
       <c r="T30">
-        <v>29.821680000000001</v>
+        <v>34.968820000000001</v>
       </c>
       <c r="U30">
-        <v>40.602229999999999</v>
+        <v>41.122970000000002</v>
       </c>
       <c r="V30">
-        <v>45.112479999999998</v>
+        <v>47.354109999999999</v>
       </c>
       <c r="X30" t="s">
         <v>20</v>
       </c>
       <c r="Y30">
-        <v>5.25</v>
+        <v>5.26</v>
       </c>
       <c r="Z30">
-        <v>5.0379999999999994</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="AA30">
-        <v>4.88</v>
+        <v>4.84</v>
       </c>
       <c r="AB30">
         <v>4.83</v>
@@ -1187,46 +1139,46 @@
         <v>8</v>
       </c>
       <c r="L31">
-        <v>8.24</v>
+        <v>7.9394400000000003</v>
       </c>
       <c r="M31">
-        <v>7.5775588512345324</v>
+        <v>7.0028699999999997</v>
       </c>
       <c r="N31">
-        <v>7.37784</v>
+        <v>6.92096</v>
       </c>
       <c r="O31">
-        <v>7.2153099999999997</v>
+        <v>7.3277400000000004</v>
       </c>
       <c r="R31" t="s">
         <v>8</v>
       </c>
       <c r="S31">
-        <v>76.175179999999997</v>
+        <v>65.42662</v>
       </c>
       <c r="T31">
-        <v>78.329400000000007</v>
+        <v>67.006690000000006</v>
       </c>
       <c r="U31">
-        <v>79.783029999999997</v>
+        <v>69.133430000000004</v>
       </c>
       <c r="V31">
-        <v>82.749390000000005</v>
+        <v>68.886799999999994</v>
       </c>
       <c r="X31" t="s">
         <v>21</v>
       </c>
       <c r="Y31">
-        <v>0.7</v>
+        <v>0.40005000000000002</v>
       </c>
       <c r="Z31">
-        <v>0.70000252109706307</v>
+        <v>0.40116000000000002</v>
       </c>
       <c r="AA31">
-        <v>0.70006999999999997</v>
+        <v>0.40848000000000001</v>
       </c>
       <c r="AB31">
-        <v>0.70001999999999998</v>
+        <v>0.40075</v>
       </c>
     </row>
     <row r="32" spans="10:32" x14ac:dyDescent="0.25">
@@ -1234,399 +1186,348 @@
         <v>10</v>
       </c>
       <c r="L32">
-        <v>8.1552600000000002</v>
+        <v>7.8417500000000002</v>
       </c>
       <c r="M32">
-        <v>7.5073438785757585</v>
+        <v>6.9263599999999999</v>
       </c>
       <c r="N32">
-        <v>7.3231599999999997</v>
+        <v>6.8425500000000001</v>
       </c>
       <c r="O32">
-        <v>7.1745299999999999</v>
+        <v>7.2614700000000001</v>
       </c>
       <c r="R32" t="s">
         <v>9</v>
       </c>
       <c r="S32">
-        <v>8.3468699999999991</v>
+        <v>11.97433</v>
       </c>
       <c r="T32">
-        <v>11.230370000000001</v>
+        <v>18.12527</v>
       </c>
       <c r="U32">
-        <v>14.25512</v>
+        <v>21.321850000000001</v>
       </c>
       <c r="V32">
-        <v>16.458030000000001</v>
+        <v>21.1721</v>
       </c>
       <c r="X32" t="s">
         <v>22</v>
       </c>
       <c r="Y32">
-        <v>5.4376899999999999</v>
+        <v>5.3896499999999996</v>
       </c>
       <c r="Z32">
-        <v>5.3582015232979883</v>
+        <v>5.8656199999999998</v>
       </c>
       <c r="AA32">
-        <v>5.5711700000000004</v>
+        <v>5.8800100000000004</v>
       </c>
       <c r="AB32">
-        <v>6.1973900000000004</v>
+        <v>5.9843099999999998</v>
       </c>
     </row>
     <row r="33" spans="10:32" x14ac:dyDescent="0.25">
       <c r="K33">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L33">
-        <v>8.1246500000000008</v>
+        <v>7.7263000000000002</v>
       </c>
       <c r="M33">
-        <v>7.4745317893238576</v>
+        <v>6.8400400000000001</v>
       </c>
       <c r="N33">
-        <v>7.3049799999999996</v>
+        <v>6.7597699999999996</v>
       </c>
       <c r="O33">
-        <v>7.1497099999999998</v>
+        <v>7.1879499999999998</v>
       </c>
       <c r="R33" t="s">
         <v>10</v>
       </c>
       <c r="S33">
-        <v>29.244969999999999</v>
+        <v>28.468990000000002</v>
       </c>
       <c r="T33">
-        <v>39.344529999999999</v>
+        <v>47.229689999999998</v>
       </c>
       <c r="U33">
-        <v>54.926729999999999</v>
+        <v>55.101210000000002</v>
       </c>
       <c r="V33">
-        <v>60.608609999999999</v>
+        <v>63.806550000000001</v>
       </c>
       <c r="X33" t="s">
         <v>23</v>
       </c>
       <c r="Y33">
-        <v>0.75</v>
+        <v>1.2057899999999999</v>
       </c>
       <c r="Z33">
-        <v>0.75005655390372228</v>
+        <v>1.29592</v>
       </c>
       <c r="AA33">
-        <v>1.0960000000000001</v>
+        <v>1.3183</v>
       </c>
       <c r="AB33">
-        <v>1.0371699999999999</v>
+        <v>1.7459899999999999</v>
       </c>
     </row>
     <row r="34" spans="10:32" x14ac:dyDescent="0.25">
       <c r="K34">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L34">
-        <v>8.0531000000000006</v>
+        <v>7.68851</v>
       </c>
       <c r="M34">
-        <v>7.4252232347610185</v>
+        <v>6.7769399999999997</v>
       </c>
       <c r="N34">
-        <v>7.26213</v>
+        <v>6.69834</v>
       </c>
       <c r="O34">
-        <v>7.0993000000000004</v>
+        <v>7.1238599999999996</v>
       </c>
       <c r="R34" t="s">
         <v>11</v>
       </c>
       <c r="S34">
-        <v>63.557139999999997</v>
+        <v>63.466810000000002</v>
       </c>
       <c r="T34">
-        <v>63.386830000000003</v>
+        <v>63.175109999999997</v>
       </c>
       <c r="U34">
-        <v>63.182369999999999</v>
+        <v>63.117829999999998</v>
       </c>
       <c r="V34">
-        <v>63.080129999999997</v>
+        <v>63.055050000000001</v>
       </c>
       <c r="X34" t="s">
         <v>26</v>
       </c>
       <c r="Y34">
-        <v>2.7610299999999999</v>
+        <v>2.3927499999999999</v>
       </c>
       <c r="Z34">
-        <v>3.0017182478681526</v>
+        <v>2.64682</v>
       </c>
       <c r="AA34">
-        <v>3.6036000000000001</v>
+        <v>2.3873000000000002</v>
       </c>
       <c r="AB34">
-        <v>3.2529400000000002</v>
+        <v>2.70465</v>
       </c>
     </row>
     <row r="35" spans="10:32" x14ac:dyDescent="0.25">
       <c r="K35">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L35">
-        <v>8.0445399999999996</v>
+        <v>7.6744899999999996</v>
       </c>
       <c r="M35">
-        <v>7.4129670130295331</v>
+        <v>6.7332299999999998</v>
       </c>
       <c r="N35">
-        <v>7.2443099999999996</v>
+        <v>6.6696999999999997</v>
       </c>
       <c r="O35">
-        <v>7.0812600000000003</v>
+        <v>7.0858600000000003</v>
       </c>
       <c r="R35" t="s">
         <v>12</v>
       </c>
       <c r="S35">
-        <v>80.448930000000004</v>
+        <v>77.225149999999999</v>
       </c>
       <c r="T35">
-        <v>80.708179999999999</v>
+        <v>78.774709999999999</v>
       </c>
       <c r="U35">
-        <v>84.419700000000006</v>
+        <v>80.956620000000001</v>
       </c>
       <c r="V35">
-        <v>88.826350000000005</v>
+        <v>89.072230000000005</v>
       </c>
       <c r="X35" t="s">
         <v>24</v>
       </c>
       <c r="Y35">
-        <v>0.50458000000000003</v>
+        <v>0.81</v>
       </c>
       <c r="Z35">
-        <v>0.52247943359597593</v>
+        <v>0.83</v>
       </c>
       <c r="AA35">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="AB35">
-        <v>0.50021000000000004</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="36" spans="10:32" x14ac:dyDescent="0.25">
       <c r="K36">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="L36">
-        <v>8.0504999999999995</v>
+        <v>7.7038599999999997</v>
       </c>
       <c r="M36">
-        <v>7.4020784811407223</v>
+        <v>6.7297599999999997</v>
       </c>
       <c r="N36">
-        <v>7.2192299999999996</v>
+        <v>6.6479200000000001</v>
       </c>
       <c r="O36">
-        <v>7.0604399999999998</v>
+        <v>7.0648799999999996</v>
       </c>
       <c r="X36" t="s">
         <v>25</v>
       </c>
       <c r="Y36">
-        <v>11.934839999999999</v>
+        <v>11.59089</v>
       </c>
       <c r="Z36">
-        <v>11.680091671013253</v>
+        <v>11.387409999999999</v>
       </c>
       <c r="AA36">
-        <v>11.455069999999999</v>
+        <v>11.41943</v>
       </c>
       <c r="AB36">
-        <v>11.542529999999999</v>
+        <v>11.291980000000001</v>
       </c>
     </row>
     <row r="37" spans="10:32" x14ac:dyDescent="0.25">
       <c r="K37">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L37">
-        <v>8.0254899999999996</v>
+        <v>7.7351400000000003</v>
       </c>
       <c r="M37">
-        <v>7.3834216959521939</v>
+        <v>6.7344799999999996</v>
       </c>
       <c r="N37">
-        <v>7.2059899999999999</v>
+        <v>6.6489099999999999</v>
       </c>
       <c r="O37">
-        <v>7.0433199999999996</v>
+        <v>7.0650700000000004</v>
       </c>
     </row>
     <row r="38" spans="10:32" x14ac:dyDescent="0.25">
       <c r="K38">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="L38">
-        <v>8.0441599999999998</v>
+        <v>7.8618800000000002</v>
       </c>
       <c r="M38">
-        <v>7.3871733367021379</v>
+        <v>6.76187</v>
       </c>
       <c r="N38">
-        <v>7.2016499999999999</v>
+        <v>6.6589299999999998</v>
       </c>
       <c r="O38">
-        <v>7.04345</v>
+        <v>7.0609099999999998</v>
       </c>
     </row>
     <row r="39" spans="10:32" x14ac:dyDescent="0.25">
       <c r="K39">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L39">
-        <v>8.0836100000000002</v>
+        <v>8.0697700000000001</v>
       </c>
       <c r="M39">
-        <v>7.4049464311515276</v>
+        <v>6.7927</v>
       </c>
       <c r="N39">
-        <v>7.1889799999999999</v>
+        <v>6.6846800000000002</v>
       </c>
       <c r="O39">
-        <v>7.0377799999999997</v>
-      </c>
-    </row>
-    <row r="40" spans="10:32" x14ac:dyDescent="0.25">
-      <c r="K40">
-        <v>28</v>
-      </c>
-      <c r="L40">
-        <v>8.1401800000000009</v>
-      </c>
-      <c r="M40">
-        <v>7.4351157426919654</v>
-      </c>
-      <c r="N40">
-        <v>7.1875600000000004</v>
-      </c>
-      <c r="O40">
-        <v>7.0311199999999996</v>
-      </c>
-    </row>
-    <row r="41" spans="10:32" x14ac:dyDescent="0.25">
-      <c r="K41">
-        <v>30</v>
-      </c>
-      <c r="L41">
-        <v>8.1766900000000007</v>
-      </c>
-      <c r="M41">
-        <v>7.4547209434987654</v>
-      </c>
-      <c r="N41">
-        <v>7.1891800000000003</v>
-      </c>
-      <c r="O41">
-        <v>7.0377200000000002</v>
-      </c>
-    </row>
-    <row r="42" spans="10:32" x14ac:dyDescent="0.25">
-      <c r="K42">
-        <v>35</v>
-      </c>
-      <c r="L42">
-        <v>8.3235499999999991</v>
-      </c>
-      <c r="M42">
-        <v>7.5061336356262522</v>
-      </c>
-      <c r="N42">
-        <v>7.2082199999999998</v>
-      </c>
-      <c r="O42">
-        <v>7.0618499999999997</v>
+        <v>7.0723500000000001</v>
       </c>
     </row>
     <row r="46" spans="10:32" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="J46" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3"/>
-      <c r="O46" s="3"/>
-      <c r="P46" s="3"/>
-      <c r="Q46" s="3"/>
-      <c r="R46" s="3"/>
-      <c r="S46" s="3"/>
-      <c r="T46" s="3"/>
-      <c r="U46" s="3"/>
-      <c r="V46" s="3"/>
-      <c r="W46" s="3"/>
-      <c r="X46" s="3"/>
-      <c r="Y46" s="3"/>
-      <c r="Z46" s="3"/>
-      <c r="AA46" s="3"/>
-      <c r="AB46" s="3"/>
-      <c r="AC46" s="3"/>
-      <c r="AD46" s="3"/>
-      <c r="AE46" s="3"/>
-      <c r="AF46" s="3"/>
+      <c r="J46" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="4"/>
+      <c r="P46" s="4"/>
+      <c r="Q46" s="4"/>
+      <c r="R46" s="4"/>
+      <c r="S46" s="4"/>
+      <c r="T46" s="4"/>
+      <c r="U46" s="4"/>
+      <c r="V46" s="4"/>
+      <c r="W46" s="4"/>
+      <c r="X46" s="4"/>
+      <c r="Y46" s="4"/>
+      <c r="Z46" s="4"/>
+      <c r="AA46" s="4"/>
+      <c r="AB46" s="4"/>
+      <c r="AC46" s="4"/>
+      <c r="AD46" s="4"/>
+      <c r="AE46" s="4"/>
+      <c r="AF46" s="4"/>
     </row>
     <row r="47" spans="10:32" x14ac:dyDescent="0.25">
       <c r="M47" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Z47" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="10:32" x14ac:dyDescent="0.25">
       <c r="K48" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L48" s="2">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="M48" s="2">
         <v>0.75</v>
       </c>
       <c r="N48" s="2">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="S48" s="2">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="T48" s="2">
         <v>0.75</v>
       </c>
       <c r="U48" s="2">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="Y48" s="2">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="Z48" s="2">
         <v>0.75</v>
       </c>
       <c r="AA48" s="2">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="49" spans="11:27" x14ac:dyDescent="0.25">
       <c r="K49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L49">
-        <v>7.9406600000000003</v>
+        <v>7.8179800000000004</v>
       </c>
       <c r="R49" t="s">
         <v>6</v>
@@ -1634,37 +1535,37 @@
     </row>
     <row r="50" spans="11:27" x14ac:dyDescent="0.25">
       <c r="K50">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="L50">
-        <v>7.7480000000000002</v>
+        <v>7.39</v>
       </c>
       <c r="M50">
-        <v>7.7447055701440242</v>
+        <v>7.37</v>
       </c>
       <c r="R50" t="s">
         <v>7</v>
       </c>
       <c r="S50">
-        <v>22.455559999999998</v>
+        <v>41.283639999999998</v>
       </c>
       <c r="T50">
-        <v>29.821680000000001</v>
+        <v>41.122970000000002</v>
       </c>
       <c r="U50">
-        <v>31.553850000000001</v>
+        <v>28.51491</v>
       </c>
       <c r="X50" t="s">
         <v>19</v>
       </c>
       <c r="Y50">
-        <v>7.3018099999999997</v>
+        <v>6.43384</v>
       </c>
       <c r="Z50">
-        <v>7.3896322613393437</v>
+        <v>6.6853800000000003</v>
       </c>
       <c r="AA50">
-        <v>4.6939399999999996</v>
+        <v>4.2084400000000004</v>
       </c>
     </row>
     <row r="51" spans="11:27" x14ac:dyDescent="0.25">
@@ -1672,34 +1573,34 @@
         <v>8</v>
       </c>
       <c r="L51">
-        <v>7.7358399999999996</v>
+        <v>7.1219400000000004</v>
       </c>
       <c r="M51">
-        <v>7.5775588512345324</v>
+        <v>6.92096</v>
       </c>
       <c r="R51" t="s">
         <v>8</v>
       </c>
       <c r="S51">
-        <v>61.280810000000002</v>
+        <v>73.552949999999996</v>
       </c>
       <c r="T51">
-        <v>78.329400000000007</v>
+        <v>69.133430000000004</v>
       </c>
       <c r="U51">
-        <v>85.905510000000007</v>
+        <v>51.259230000000002</v>
       </c>
       <c r="X51" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Y51">
-        <v>5</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="Z51">
-        <v>5.0379999999999994</v>
+        <v>4.84</v>
       </c>
       <c r="AA51">
-        <v>5.0199999999999996</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="52" spans="11:27" x14ac:dyDescent="0.25">
@@ -1707,273 +1608,231 @@
         <v>10</v>
       </c>
       <c r="L52">
-        <v>7.6704499999999998</v>
+        <v>7.1001500000000002</v>
       </c>
       <c r="M52">
-        <v>7.5073438785757585</v>
+        <v>6.8425500000000001</v>
       </c>
       <c r="N52">
-        <v>7.9923000000000002</v>
+        <v>7.9039999999999999</v>
       </c>
       <c r="R52" t="s">
         <v>9</v>
       </c>
       <c r="S52">
-        <v>6.4889799999999997</v>
+        <v>19.630469999999999</v>
       </c>
       <c r="T52">
-        <v>11.230370000000001</v>
+        <v>21.321850000000001</v>
       </c>
       <c r="U52">
-        <v>12.85088</v>
+        <v>13.54368</v>
       </c>
       <c r="X52" t="s">
         <v>21</v>
       </c>
       <c r="Y52">
-        <v>0.70003000000000004</v>
+        <v>0.40134999999999998</v>
       </c>
       <c r="Z52">
-        <v>0.70000252109706307</v>
+        <v>0.40848000000000001</v>
       </c>
       <c r="AA52">
-        <v>0.70006000000000002</v>
+        <v>0.67728999999999995</v>
       </c>
     </row>
     <row r="53" spans="11:27" x14ac:dyDescent="0.25">
       <c r="K53">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L53">
-        <v>7.6541300000000003</v>
+        <v>7.0513399999999997</v>
       </c>
       <c r="M53">
-        <v>7.4745317893238576</v>
+        <v>6.7597699999999996</v>
       </c>
       <c r="N53">
-        <v>7.6649200000000004</v>
+        <v>6.86</v>
       </c>
       <c r="R53" t="s">
         <v>10</v>
       </c>
       <c r="S53">
-        <v>38.983440000000002</v>
+        <v>55.190739999999998</v>
       </c>
       <c r="T53">
-        <v>39.344529999999999</v>
+        <v>55.101210000000002</v>
       </c>
       <c r="U53">
-        <v>39.480350000000001</v>
+        <v>54.042059999999999</v>
       </c>
       <c r="X53" t="s">
         <v>22</v>
       </c>
       <c r="Y53">
-        <v>5.3839300000000003</v>
+        <v>5.80694</v>
       </c>
       <c r="Z53">
-        <v>5.3582015232979883</v>
+        <v>5.8800100000000004</v>
       </c>
       <c r="AA53">
-        <v>2.8418700000000001</v>
+        <v>3.56969</v>
       </c>
     </row>
     <row r="54" spans="11:27" x14ac:dyDescent="0.25">
       <c r="K54">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L54">
-        <v>7.6345900000000002</v>
+        <v>7.0134400000000001</v>
       </c>
       <c r="M54">
-        <v>7.4252232347610185</v>
+        <v>6.69834</v>
       </c>
       <c r="N54">
-        <v>7.5909800000000001</v>
+        <v>6.7496700000000001</v>
       </c>
       <c r="R54" t="s">
         <v>11</v>
       </c>
       <c r="S54">
-        <v>61.819450000000003</v>
+        <v>66.552220000000005</v>
       </c>
       <c r="T54">
-        <v>63.386830000000003</v>
+        <v>63.117829999999998</v>
       </c>
       <c r="U54">
-        <v>65.475359999999995</v>
+        <v>60.456870000000002</v>
       </c>
       <c r="X54" t="s">
         <v>23</v>
       </c>
       <c r="Y54">
-        <v>0.95296999999999998</v>
+        <v>1.8189299999999999</v>
       </c>
       <c r="Z54">
-        <v>0.75005655390372228</v>
+        <v>1.3183</v>
       </c>
       <c r="AA54">
-        <v>0.75022</v>
+        <v>0.75043000000000004</v>
       </c>
     </row>
     <row r="55" spans="11:27" x14ac:dyDescent="0.25">
       <c r="K55">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L55">
-        <v>7.6241599999999998</v>
+        <v>7.0009800000000002</v>
       </c>
       <c r="M55">
-        <v>7.4129670130295331</v>
+        <v>6.6696999999999997</v>
       </c>
       <c r="N55">
-        <v>7.5235000000000003</v>
+        <v>6.6952499999999997</v>
       </c>
       <c r="R55" t="s">
         <v>12</v>
       </c>
       <c r="S55">
-        <v>82.668599999999998</v>
+        <v>80.546120000000002</v>
       </c>
       <c r="T55">
-        <v>80.708179999999999</v>
+        <v>80.956620000000001</v>
       </c>
       <c r="U55">
-        <v>80.133589999999998</v>
+        <v>83.524889999999999</v>
       </c>
       <c r="X55" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Y55">
-        <v>3.476</v>
+        <v>3.3773499999999999</v>
       </c>
       <c r="Z55">
-        <v>3.0017182478681526</v>
+        <v>2.3873000000000002</v>
       </c>
       <c r="AA55">
-        <v>2.8350300000000002</v>
+        <v>2.1574800000000001</v>
       </c>
     </row>
     <row r="56" spans="11:27" x14ac:dyDescent="0.25">
       <c r="K56">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="L56">
-        <v>7.6099899999999998</v>
+        <v>6.9945500000000003</v>
       </c>
       <c r="M56">
-        <v>7.4020784811407223</v>
+        <v>6.6479200000000001</v>
       </c>
       <c r="N56">
-        <v>7.4677100000000003</v>
+        <v>6.6943400000000004</v>
       </c>
       <c r="X56" t="s">
         <v>24</v>
       </c>
       <c r="Y56">
-        <v>0.74392000000000003</v>
+        <v>1.68</v>
       </c>
       <c r="Z56">
-        <v>0.52247943359597593</v>
+        <v>0.83</v>
       </c>
       <c r="AA56">
-        <v>0.50000999999999995</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="57" spans="11:27" x14ac:dyDescent="0.25">
       <c r="K57">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L57">
-        <v>7.5983700000000001</v>
+        <v>6.99458</v>
       </c>
       <c r="M57">
-        <v>7.3834216959521939</v>
+        <v>6.6489099999999999</v>
       </c>
       <c r="N57">
-        <v>7.4721900000000003</v>
+        <v>6.6981799999999998</v>
       </c>
       <c r="X57" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Y57">
-        <v>12.36124</v>
+        <v>11.455830000000001</v>
       </c>
       <c r="Z57">
-        <v>11.680091671013253</v>
+        <v>11.41943</v>
       </c>
       <c r="AA57">
-        <v>8.8547200000000004</v>
+        <v>8.1884499999999996</v>
       </c>
     </row>
     <row r="58" spans="11:27" x14ac:dyDescent="0.25">
       <c r="K58">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="L58">
-        <v>7.6003600000000002</v>
+        <v>7.0139800000000001</v>
       </c>
       <c r="M58">
-        <v>7.3871733367021379</v>
+        <v>6.6589299999999998</v>
       </c>
       <c r="N58">
-        <v>7.4737900000000002</v>
+        <v>6.7165100000000004</v>
       </c>
     </row>
     <row r="59" spans="11:27" x14ac:dyDescent="0.25">
       <c r="K59">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L59">
-        <v>7.6129800000000003</v>
+        <v>7.0244499999999999</v>
       </c>
       <c r="M59">
-        <v>7.4049464311515276</v>
+        <v>6.6846800000000002</v>
       </c>
       <c r="N59">
-        <v>7.4914199999999997</v>
-      </c>
-    </row>
-    <row r="60" spans="11:27" x14ac:dyDescent="0.25">
-      <c r="K60">
-        <v>28</v>
-      </c>
-      <c r="L60">
-        <v>7.6334900000000001</v>
-      </c>
-      <c r="M60">
-        <v>7.4351157426919654</v>
-      </c>
-      <c r="N60">
-        <v>7.4869000000000003</v>
-      </c>
-    </row>
-    <row r="61" spans="11:27" x14ac:dyDescent="0.25">
-      <c r="K61">
-        <v>30</v>
-      </c>
-      <c r="L61">
-        <v>7.6520799999999998</v>
-      </c>
-      <c r="M61">
-        <v>7.4547209434987654</v>
-      </c>
-      <c r="N61">
-        <v>7.5081600000000002</v>
-      </c>
-    </row>
-    <row r="62" spans="11:27" x14ac:dyDescent="0.25">
-      <c r="K62">
-        <v>35</v>
-      </c>
-      <c r="L62">
-        <v>7.70282</v>
-      </c>
-      <c r="M62">
-        <v>7.5061336356262522</v>
-      </c>
-      <c r="N62">
-        <v>7.5670000000000002</v>
+        <v>6.7274000000000003</v>
       </c>
     </row>
   </sheetData>
